--- a/Layout_Asegurados_template.xlsx
+++ b/Layout_Asegurados_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ATENCION ELITE\Dropbox\Ü HEALTH\Ü\AP\2025 - 2026  THONA\MOVIMIENTOS\MOV 36 ALTA - 6732\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tecno\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{672DC730-A61C-474A-AEC9-6C8D8BFCA51B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3452D57E-D60F-40CD-BBE8-D908E5143BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-107" yWindow="-107" windowWidth="20847" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>CARGA DE ASEGURADOS</t>
   </si>
@@ -75,90 +75,6 @@
   <si>
     <t>Sueldo Mensual
  o Saldo Insoluto o Monto de Suma Asegurada</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>JOSE DE JESUS</t>
-  </si>
-  <si>
-    <t>SALGADO</t>
-  </si>
-  <si>
-    <t>SERVIN</t>
-  </si>
-  <si>
-    <t>ALMA DELIA</t>
-  </si>
-  <si>
-    <t>ANTILLON</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>JOSE ANGEL</t>
-  </si>
-  <si>
-    <t>URUETA</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>ANA GABRIELA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>MIA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>LOYA</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>SAUL SEBASTIAN</t>
-  </si>
-  <si>
-    <t>DIZAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>CHACON</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
-    <t>HINOJOS</t>
-  </si>
-  <si>
-    <t>EDUARDO ALONSO</t>
-  </si>
-  <si>
-    <t>M</t>
   </si>
 </sst>
 </file>
@@ -560,25 +476,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="15.05" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7265625" customWidth="1"/>
-    <col min="2" max="2" width="24.36328125" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" customWidth="1"/>
-    <col min="4" max="4" width="10.08984375" customWidth="1"/>
-    <col min="5" max="5" width="20.36328125" style="13" customWidth="1"/>
-    <col min="6" max="6" width="20.36328125" customWidth="1"/>
-    <col min="7" max="7" width="15.7265625" customWidth="1"/>
-    <col min="8" max="8" width="24.6328125" customWidth="1"/>
-    <col min="9" max="12" width="12.08984375" customWidth="1"/>
+    <col min="1" max="1" width="10.75" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" customWidth="1"/>
+    <col min="3" max="3" width="12.25" customWidth="1"/>
+    <col min="4" max="4" width="10.08203125" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" style="13" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" customWidth="1"/>
+    <col min="7" max="7" width="15.75" customWidth="1"/>
+    <col min="8" max="8" width="24.6640625" customWidth="1"/>
+    <col min="9" max="12" width="12.08203125" customWidth="1"/>
     <col min="13" max="26" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16"/>
       <c r="B1" s="17"/>
     </row>
-    <row r="2" spans="1:12" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="G2" s="18" t="s">
@@ -586,19 +502,19 @@
       </c>
       <c r="H2" s="17"/>
     </row>
-    <row r="3" spans="1:12" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:12" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:12" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="4" t="s">
         <v>1</v>
@@ -606,7 +522,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:12" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="4" t="s">
         <v>2</v>
@@ -614,7 +530,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:12" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
         <v>3</v>
@@ -622,19 +538,19 @@
       <c r="G7" s="2"/>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:12" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="G8" s="2"/>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:12" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="G9" s="2"/>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:12" ht="66.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>4</v>
       </c>
@@ -662,249 +578,62 @@
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
     </row>
-    <row r="11" spans="1:12" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>1</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="12">
-        <v>25068</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>38</v>
-      </c>
+    <row r="11" spans="1:12" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E11"/>
       <c r="G11" s="10"/>
       <c r="H11" s="11"/>
     </row>
-    <row r="12" spans="1:12" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
-        <v>1</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="12">
-        <v>24726</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>11</v>
-      </c>
+    <row r="12" spans="1:12" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E12"/>
       <c r="G12" s="10"/>
       <c r="H12" s="11"/>
     </row>
-    <row r="13" spans="1:12" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
-        <v>1</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="12">
-        <v>23194</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>38</v>
-      </c>
+    <row r="13" spans="1:12" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E13"/>
       <c r="G13" s="10"/>
       <c r="H13" s="11"/>
     </row>
-    <row r="14" spans="1:12" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
-        <v>1</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="12">
-        <v>29249</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>11</v>
-      </c>
+    <row r="14" spans="1:12" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E14"/>
       <c r="G14" s="10"/>
       <c r="H14" s="11"/>
     </row>
-    <row r="15" spans="1:12" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
-        <v>1</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="12">
-        <v>25154</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>38</v>
-      </c>
+    <row r="15" spans="1:12" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E15"/>
       <c r="G15" s="10"/>
       <c r="H15" s="11"/>
     </row>
-    <row r="16" spans="1:12" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
-        <v>1</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="12">
-        <v>31855</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>11</v>
-      </c>
+    <row r="16" spans="1:12" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E16"/>
       <c r="G16" s="10"/>
       <c r="H16" s="11"/>
     </row>
-    <row r="17" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
-        <v>1</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="12">
-        <v>39053</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>11</v>
-      </c>
+    <row r="17" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E17"/>
       <c r="G17" s="10"/>
       <c r="H17" s="11"/>
     </row>
-    <row r="18" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
-        <v>1</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" s="12">
-        <v>38599</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>38</v>
-      </c>
+    <row r="18" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E18"/>
       <c r="G18" s="10"/>
       <c r="H18" s="11"/>
     </row>
-    <row r="19" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
-        <v>1</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" s="12">
-        <v>34218</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>38</v>
-      </c>
+    <row r="19" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E19"/>
       <c r="G19" s="10"/>
       <c r="H19" s="11"/>
     </row>
-    <row r="20" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
-        <v>1</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" s="12">
-        <v>33666</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>11</v>
-      </c>
+    <row r="20" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E20"/>
       <c r="G20" s="10"/>
       <c r="H20" s="11"/>
     </row>
-    <row r="21" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
-        <v>1</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21" s="12">
-        <v>29975</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>11</v>
-      </c>
+    <row r="21" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E21"/>
       <c r="G21" s="10"/>
       <c r="H21" s="11"/>
     </row>
-    <row r="22" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -914,7 +643,7 @@
       <c r="G22" s="10"/>
       <c r="H22" s="11"/>
     </row>
-    <row r="23" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -924,7 +653,7 @@
       <c r="G23" s="10"/>
       <c r="H23" s="11"/>
     </row>
-    <row r="24" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -934,7 +663,7 @@
       <c r="G24" s="10"/>
       <c r="H24" s="11"/>
     </row>
-    <row r="25" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -944,7 +673,7 @@
       <c r="G25" s="10"/>
       <c r="H25" s="11"/>
     </row>
-    <row r="26" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -954,7 +683,7 @@
       <c r="G26" s="10"/>
       <c r="H26" s="11"/>
     </row>
-    <row r="27" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -964,7 +693,7 @@
       <c r="G27" s="10"/>
       <c r="H27" s="11"/>
     </row>
-    <row r="28" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -974,7 +703,7 @@
       <c r="G28" s="10"/>
       <c r="H28" s="11"/>
     </row>
-    <row r="29" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -984,7 +713,7 @@
       <c r="G29" s="10"/>
       <c r="H29" s="11"/>
     </row>
-    <row r="30" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -994,7 +723,7 @@
       <c r="G30" s="10"/>
       <c r="H30" s="11"/>
     </row>
-    <row r="31" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -1004,7 +733,7 @@
       <c r="G31" s="10"/>
       <c r="H31" s="11"/>
     </row>
-    <row r="32" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -1014,7 +743,7 @@
       <c r="G32" s="10"/>
       <c r="H32" s="11"/>
     </row>
-    <row r="33" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -1024,7 +753,7 @@
       <c r="G33" s="10"/>
       <c r="H33" s="11"/>
     </row>
-    <row r="34" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -1034,7 +763,7 @@
       <c r="G34" s="10"/>
       <c r="H34" s="11"/>
     </row>
-    <row r="35" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -1044,7 +773,7 @@
       <c r="G35" s="10"/>
       <c r="H35" s="11"/>
     </row>
-    <row r="36" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
@@ -1054,7 +783,7 @@
       <c r="G36" s="10"/>
       <c r="H36" s="11"/>
     </row>
-    <row r="37" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -1064,7 +793,7 @@
       <c r="G37" s="10"/>
       <c r="H37" s="11"/>
     </row>
-    <row r="38" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -1074,7 +803,7 @@
       <c r="G38" s="10"/>
       <c r="H38" s="11"/>
     </row>
-    <row r="39" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -1084,7 +813,7 @@
       <c r="G39" s="10"/>
       <c r="H39" s="11"/>
     </row>
-    <row r="40" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="15"/>
       <c r="C40" s="15"/>
@@ -1094,7 +823,7 @@
       <c r="G40" s="10"/>
       <c r="H40" s="11"/>
     </row>
-    <row r="41" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -1104,7 +833,7 @@
       <c r="G41" s="10"/>
       <c r="H41" s="11"/>
     </row>
-    <row r="42" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -1114,7 +843,7 @@
       <c r="G42" s="10"/>
       <c r="H42" s="11"/>
     </row>
-    <row r="43" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -1124,7 +853,7 @@
       <c r="G43" s="10"/>
       <c r="H43" s="11"/>
     </row>
-    <row r="44" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -1134,7 +863,7 @@
       <c r="G44" s="10"/>
       <c r="H44" s="11"/>
     </row>
-    <row r="45" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -1144,7 +873,7 @@
       <c r="G45" s="10"/>
       <c r="H45" s="11"/>
     </row>
-    <row r="46" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -1154,7 +883,7 @@
       <c r="G46" s="10"/>
       <c r="H46" s="11"/>
     </row>
-    <row r="47" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
@@ -1164,7 +893,7 @@
       <c r="G47" s="10"/>
       <c r="H47" s="11"/>
     </row>
-    <row r="48" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -1174,7 +903,7 @@
       <c r="G48" s="10"/>
       <c r="H48" s="11"/>
     </row>
-    <row r="49" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
@@ -1184,7 +913,7 @@
       <c r="G49" s="10"/>
       <c r="H49" s="11"/>
     </row>
-    <row r="50" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
@@ -1194,7 +923,7 @@
       <c r="G50" s="10"/>
       <c r="H50" s="11"/>
     </row>
-    <row r="51" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
@@ -1204,7 +933,7 @@
       <c r="G51" s="10"/>
       <c r="H51" s="11"/>
     </row>
-    <row r="52" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="15"/>
       <c r="C52" s="15"/>
@@ -1214,7 +943,7 @@
       <c r="G52" s="10"/>
       <c r="H52" s="11"/>
     </row>
-    <row r="53" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="15"/>
       <c r="C53" s="15"/>
@@ -1224,7 +953,7 @@
       <c r="G53" s="10"/>
       <c r="H53" s="11"/>
     </row>
-    <row r="54" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="15"/>
       <c r="C54" s="15"/>
@@ -1234,7 +963,7 @@
       <c r="G54" s="10"/>
       <c r="H54" s="11"/>
     </row>
-    <row r="55" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -1244,7 +973,7 @@
       <c r="G55" s="10"/>
       <c r="H55" s="11"/>
     </row>
-    <row r="56" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
@@ -1254,7 +983,7 @@
       <c r="G56" s="10"/>
       <c r="H56" s="11"/>
     </row>
-    <row r="57" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -1264,7 +993,7 @@
       <c r="G57" s="10"/>
       <c r="H57" s="11"/>
     </row>
-    <row r="58" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="15"/>
       <c r="C58" s="15"/>
@@ -1274,7 +1003,7 @@
       <c r="G58" s="10"/>
       <c r="H58" s="11"/>
     </row>
-    <row r="59" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
@@ -1284,7 +1013,7 @@
       <c r="G59" s="10"/>
       <c r="H59" s="11"/>
     </row>
-    <row r="60" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="15"/>
       <c r="C60" s="15"/>
@@ -1294,7 +1023,7 @@
       <c r="G60" s="10"/>
       <c r="H60" s="11"/>
     </row>
-    <row r="61" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
@@ -1304,7 +1033,7 @@
       <c r="G61" s="10"/>
       <c r="H61" s="11"/>
     </row>
-    <row r="62" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
@@ -1314,7 +1043,7 @@
       <c r="G62" s="10"/>
       <c r="H62" s="11"/>
     </row>
-    <row r="63" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="15"/>
       <c r="C63" s="15"/>
@@ -1324,7 +1053,7 @@
       <c r="G63" s="10"/>
       <c r="H63" s="11"/>
     </row>
-    <row r="64" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
@@ -1334,7 +1063,7 @@
       <c r="G64" s="10"/>
       <c r="H64" s="11"/>
     </row>
-    <row r="65" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="15"/>
       <c r="C65" s="15"/>
@@ -1344,7 +1073,7 @@
       <c r="G65" s="10"/>
       <c r="H65" s="11"/>
     </row>
-    <row r="66" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
@@ -1354,7 +1083,7 @@
       <c r="G66" s="10"/>
       <c r="H66" s="11"/>
     </row>
-    <row r="67" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="15"/>
       <c r="C67" s="15"/>
@@ -1364,7 +1093,7 @@
       <c r="G67" s="10"/>
       <c r="H67" s="11"/>
     </row>
-    <row r="68" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="15"/>
       <c r="C68" s="15"/>
@@ -1374,7 +1103,7 @@
       <c r="G68" s="10"/>
       <c r="H68" s="11"/>
     </row>
-    <row r="69" spans="1:8" ht="13.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="15"/>
       <c r="C69" s="15"/>
